--- a/healthcare_forms/013_telemedicine_consultant_evaluation_form--healthcare_forms.xlsx
+++ b/healthcare_forms/013_telemedicine_consultant_evaluation_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_0,_'name':_'excellent',_'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 0, 'name': 'Excellent', 'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'good',_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Good', 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'fair',_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Fair', 'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'poor',_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Poor', 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_0,_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 0, 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'undecided',_'label':_'undecided'}</t>
+          <t>undecided</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Undecided', 'label': 'Undecided'}</t>
+          <t>Undecided</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_0,_'name':_'less_than_once_a_month',_'label':_'less_than_once_a_month'}</t>
+          <t>less_than_once_a_month</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 0, 'name': 'Less than once a month', 'label': 'Less than once a month'}</t>
+          <t>Less than once a month</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'once_a_month',_'label':_'once_a_month'}</t>
+          <t>once_a_month</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Once a month', 'label': 'Once a month'}</t>
+          <t>Once a month</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'multiple_times_a_month',_'label':_'multiple_times_a_month'}</t>
+          <t>multiple_times_a_month</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Multiple times a month', 'label': 'Multiple times a month'}</t>
+          <t>Multiple times a month</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'more_than_once_a_week',_'label':_'more_than_once_a_week'}</t>
+          <t>more_than_once_a_week</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'More than once a week', 'label': 'More than once a week'}</t>
+          <t>More than once a week</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_0,_'name':_'primary_care_physician',_'label':_'primary_care_physician'}</t>
+          <t>primary_care_physician</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 0, 'name': 'Primary Care Physician', 'label': 'Primary Care Physician'}</t>
+          <t>Primary Care Physician</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'specialist',_'label':_'specialist'}</t>
+          <t>specialist</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Specialist', 'label': 'Specialist'}</t>
+          <t>Specialist</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'multiple',_'label':_'multiple'}</t>
+          <t>multiple</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Multiple', 'label': 'Multiple'}</t>
+          <t>Multiple</t>
         </is>
       </c>
     </row>
